--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25207"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9067E696-2033-4915-A9AF-4D6AB3A8BA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD4569E3-AEAC-44FB-B439-BAB819964D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="95">
   <si>
     <t>Имя теста</t>
   </si>
@@ -53,114 +53,153 @@
     <t>2. Отправить GET-запрос на эндпоинт /bear</t>
   </si>
   <si>
-    <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content шага 1.</t>
-  </si>
-  <si>
-    <t>2. Получить список медведей</t>
+    <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content в шаге 1.</t>
+  </si>
+  <si>
+    <t>3. Отправить POST-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"BROWN","bear_name":"mikhail","bear_age":17.5}</t>
+  </si>
+  <si>
+    <t>4. Отправить GET-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content в шаге 3.</t>
+  </si>
+  <si>
+    <t>5. Отправить POST-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"POLAR","bear_name":"mikhail","bear_age":17.5}</t>
+  </si>
+  <si>
+    <t>6. Отправить GET-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content в шаге 5.</t>
+  </si>
+  <si>
+    <t>7. Отправить POST-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"GUMMY","bear_name":"mikhail","bear_age":17.5}</t>
+  </si>
+  <si>
+    <t>8. Отправить GET-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content в шаге 6.</t>
+  </si>
+  <si>
+    <t>3. Получить запись о медведе</t>
+  </si>
+  <si>
+    <t>Предусловие: существует медведь с bear_id = ID</t>
+  </si>
+  <si>
+    <t>1. Отправить GET-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - json с bear_id = ID.</t>
+  </si>
+  <si>
+    <t>4. Обновить запись о медведе</t>
+  </si>
+  <si>
+    <t>1. Отправить PUT-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - сообщение-подтверждение.</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"BLACK","bear_name":"test_name","bear_age":1.5}</t>
+  </si>
+  <si>
+    <t>2. Отправить GET-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 1 и bear_id = ID.</t>
+  </si>
+  <si>
+    <t>3. Отправить PUT-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"BROWN","bear_name":"test_name","bear_age":1.5}</t>
+  </si>
+  <si>
+    <t>4. Отправить GET-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 3 и bear_id = ID.</t>
+  </si>
+  <si>
+    <t>5. Отправить PUT-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"POLAR","bear_name":"test_name","bear_age":1.5}</t>
+  </si>
+  <si>
+    <t>6. Отправить GET-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 5 и bear_id = ID.</t>
+  </si>
+  <si>
+    <t>7. Отправить PUT-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"GUMMY","bear_name":"test_name","bear_age":1.5}</t>
+  </si>
+  <si>
+    <t>8. Отправить GET-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 7 и bear_id = ID.</t>
+  </si>
+  <si>
+    <t>5. Удалить записи о всех медведях</t>
+  </si>
+  <si>
+    <t>Предусловие: существует хотя бы 1 медведь</t>
+  </si>
+  <si>
+    <t>1. Отправить DELETE-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - сообщение-подтверждение</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content пустой список в формате JSON.</t>
+  </si>
+  <si>
+    <t>6. Удалить запись о медведе</t>
+  </si>
+  <si>
+    <t>1. Отправить DELETE-запрос на эндпоинт /bear/ID</t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content нет медведя с bear_id, равным ID</t>
+  </si>
+  <si>
+    <t>7. Получить несуществующую запись о медведе</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предусловие: медведя с bear_id = ID не существует </t>
+  </si>
+  <si>
+    <t>Ответ: статус код HTTP - 200, в Content - сообщение, что записи нет</t>
+  </si>
+  <si>
+    <t>8. Получить пустой список медведей</t>
+  </si>
+  <si>
+    <t>Предусловие: записей о медведях нет</t>
   </si>
   <si>
     <t>1. Отправить GET-запрос на эндпоинт /bear</t>
   </si>
   <si>
-    <t>Ответ: статус код HTTP - 200, Content в формате json</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, Content в формате json и равен content из шага 1</t>
-  </si>
-  <si>
-    <t>3. Получить запись о медведе</t>
-  </si>
-  <si>
-    <t>Предусловие: существует медведь с bear_id = ID</t>
-  </si>
-  <si>
-    <t>1. Отправить GET-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - json с bear_id = ID.</t>
-  </si>
-  <si>
-    <t>2. Отправить GET-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>4. Обновить запись о медведе</t>
-  </si>
-  <si>
-    <t>1. Отправить PUT-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - сообщение-подтверждение.</t>
-  </si>
-  <si>
-    <t>payload {"bear_type":"BROWN","bear_name":"test_name","bear_age":1.5}</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 1 и bear_id = ID.</t>
-  </si>
-  <si>
-    <t>3. Отправить PUT-запрос на эндпоинт /bear/ID с payload шага 1</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 2XX, в Content - сообщение-подтверждение.</t>
-  </si>
-  <si>
-    <t>4. Отправить GET-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - json, запись о медведе должны быть такой же как и в шаге 2</t>
-  </si>
-  <si>
-    <t>5. Удалить записи о всех медведях</t>
-  </si>
-  <si>
-    <t>Предусловие: существует хотя бы 1 медведь</t>
-  </si>
-  <si>
-    <t>1. Отправить DELETE-запрос на эндпоинт /bear</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - сообщение-подтверждение</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content пустой список в формате JSON.</t>
-  </si>
-  <si>
-    <t>3. Отправить DELETE-запрос на эндпоинт /bear</t>
-  </si>
-  <si>
-    <t>4. Отправить GET-запрос на эндпоинт /bear</t>
-  </si>
-  <si>
-    <t>6. Удалить запись о медведе</t>
-  </si>
-  <si>
-    <t>1. Отправить DELETE-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content нет медведя с bear_id, равным ID</t>
-  </si>
-  <si>
-    <t>3. Отправить DELETE-запрос на эндпоинт /bear/ID</t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content должен быть таким же как в шаге 2</t>
-  </si>
-  <si>
-    <t>7. Получить несуществующую запись о медведе</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предусловие: медведя с bear_id = ID не существует </t>
-  </si>
-  <si>
-    <t>Ответ: статус код HTTP - 200, в Content - сообщение, что записи нет</t>
-  </si>
-  <si>
-    <t>8. Получить пустой список медведей</t>
-  </si>
-  <si>
-    <t>Предусловие: записей о медведях нет</t>
-  </si>
-  <si>
     <t>9. Обновить запись несуществующего медведя</t>
   </si>
   <si>
@@ -192,6 +231,15 @@
   </si>
   <si>
     <t>payload {"bear_type":"BROWN","bear_name":"Test bear name","bear_age":"FALSE"}</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"BROWN","bear_name":"Test bear name","bear_age":0}</t>
+  </si>
+  <si>
+    <t>4. Отправить POST-запрос на эндпоинт /bear</t>
+  </si>
+  <si>
+    <t>payload {"bear_type":"BROWN","bear_name":"Test bear name","bear_age":-10}</t>
   </si>
   <si>
     <t>14. Создать медведя с лишними полями</t>
@@ -615,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="75.7109375" bestFit="1" customWidth="1"/>
@@ -658,29 +706,36 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -698,58 +753,55 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
       <c r="B13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
+    <row r="19" spans="1:3">
+      <c r="B19" t="s">
         <v>26</v>
       </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -764,456 +816,529 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" t="s">
         <v>32</v>
       </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="B27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="B33" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
       <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
       <c r="B38" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>45</v>
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
       <c r="B40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" t="s">
         <v>46</v>
       </c>
-      <c r="B42" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="B43" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="B46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="B49" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="B52" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
       <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="B54" t="s">
-        <v>54</v>
+        <v>45</v>
+      </c>
+      <c r="C54" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="B57" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="B60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="B61" t="s">
-        <v>50</v>
+        <v>66</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="B62" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>60</v>
-      </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="B64" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="B65" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="B66" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="B67" t="s">
-        <v>54</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>62</v>
-      </c>
       <c r="B69" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="B70" t="s">
-        <v>19</v>
-      </c>
-      <c r="C70" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="B73" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="B71" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>64</v>
-      </c>
-      <c r="B73" t="s">
-        <v>4</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
-      </c>
-      <c r="C75" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="B76" t="s">
-        <v>66</v>
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="B77" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>67</v>
-      </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="C78" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="B79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
-      </c>
-      <c r="C81" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="B82" t="s">
-        <v>70</v>
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="B83" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="B86" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>81</v>
+      </c>
       <c r="B87" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
-        <v>75</v>
-      </c>
-      <c r="B89" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="B88" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>83</v>
+      </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
-        <v>76</v>
-      </c>
-      <c r="B92" t="s">
-        <v>14</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="B91" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>85</v>
+      </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="B94" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96" t="s">
-        <v>14</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="B95" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>87</v>
+      </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="B98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
-        <v>78</v>
-      </c>
-      <c r="B100" t="s">
-        <v>14</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="B99" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>91</v>
+      </c>
       <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="B102" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="B106" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>93</v>
+      </c>
+      <c r="B108" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="B110" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>94</v>
+      </c>
+      <c r="B112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="B114" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="B115" t="s">
         <v>6</v>
       </c>
     </row>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25207"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD4569E3-AEAC-44FB-B439-BAB819964D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E0A8CF1-EDFB-40C2-BFEA-EED07811A194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
     <t>Ответ: статус код HTTP - 200, в Content есть медведь с bear_id, полученный в Content в шаге 6.</t>
   </si>
   <si>
-    <t>3. Получить запись о медведе</t>
+    <t>2. Получить запись о медведе</t>
   </si>
   <si>
     <t>Предусловие: существует медведь с bear_id = ID</t>
@@ -104,7 +104,7 @@
     <t>Ответ: статус код HTTP - 200, в Content - json с bear_id = ID.</t>
   </si>
   <si>
-    <t>4. Обновить запись о медведе</t>
+    <t>3. Обновить запись о медведе</t>
   </si>
   <si>
     <t>1. Отправить PUT-запрос на эндпоинт /bear/ID</t>
@@ -158,7 +158,7 @@
     <t>Ответ: статус код HTTP - 200, в Content - json, отправленный на шаге 7 и bear_id = ID.</t>
   </si>
   <si>
-    <t>5. Удалить записи о всех медведях</t>
+    <t>4. Удалить записи о всех медведях</t>
   </si>
   <si>
     <t>Предусловие: существует хотя бы 1 медведь</t>
@@ -173,7 +173,7 @@
     <t>Ответ: статус код HTTP - 200, в Content пустой список в формате JSON.</t>
   </si>
   <si>
-    <t>6. Удалить запись о медведе</t>
+    <t>5. Удалить запись о медведе</t>
   </si>
   <si>
     <t>1. Отправить DELETE-запрос на эндпоинт /bear/ID</t>
@@ -182,7 +182,7 @@
     <t>Ответ: статус код HTTP - 200, в Content нет медведя с bear_id, равным ID</t>
   </si>
   <si>
-    <t>7. Получить несуществующую запись о медведе</t>
+    <t>6. Получить несуществующую запись о медведе</t>
   </si>
   <si>
     <t xml:space="preserve">Предусловие: медведя с bear_id = ID не существует </t>
@@ -191,7 +191,7 @@
     <t>Ответ: статус код HTTP - 200, в Content - сообщение, что записи нет</t>
   </si>
   <si>
-    <t>8. Получить пустой список медведей</t>
+    <t>7. Получить пустой список медведей</t>
   </si>
   <si>
     <t>Предусловие: записей о медведях нет</t>
@@ -200,19 +200,19 @@
     <t>1. Отправить GET-запрос на эндпоинт /bear</t>
   </si>
   <si>
-    <t>9. Обновить запись несуществующего медведя</t>
+    <t>8. Обновить запись несуществующего медведя</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 404</t>
   </si>
   <si>
-    <t>10. Удалить запись несуществующего медведя</t>
-  </si>
-  <si>
-    <t>11. Удалить несуществующие записи о всех медведях</t>
-  </si>
-  <si>
-    <t>12. Создать медведя с частично заполненными обязательными полями</t>
+    <t>9. Удалить запись несуществующего медведя</t>
+  </si>
+  <si>
+    <t>10. Удалить несуществующие записи о всех медведях</t>
+  </si>
+  <si>
+    <t>11. Создать медведя с частично заполненными обязательными полями</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 200, в Content - сообщение об ошибке, медведь не должен быть создан</t>
@@ -221,7 +221,7 @@
     <t>payload {"bear_name":"mikhail"}</t>
   </si>
   <si>
-    <t>13. Создать медведя с частично неверными полями</t>
+    <t>12. Создать медведя с частично неверными полями</t>
   </si>
   <si>
     <t>payload {"bear_type":"GIANT","bear_name":"Test bear name","bear_age":15.1}</t>
@@ -242,7 +242,7 @@
     <t>payload {"bear_type":"BROWN","bear_name":"Test bear name","bear_age":-10}</t>
   </si>
   <si>
-    <t>14. Создать медведя с лишними полями</t>
+    <t>13. Создать медведя с лишними полями</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 201, в Content - число, равное ID созданного медведя, медведь должен быть создан без лишних полей</t>
@@ -251,46 +251,46 @@
     <t>payload {"Qwe": "asd", "bear_type":"BLACK","bear_name":"mikhail","bear_age":17.5}</t>
   </si>
   <si>
-    <t>15. Обновить запись медведя частично заполненными обязательными полями</t>
+    <t>14. Обновить запись медведя частично заполненными обязательными полями</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 200, в Content - сообщение об ошибке, запись о медведе не должна измениться</t>
   </si>
   <si>
-    <t>16. Обновить запись медведя частично неверными полями</t>
+    <t>15. Обновить запись медведя частично неверными полями</t>
   </si>
   <si>
     <t>2. Отправить PUT-запрос на эндпоинт /bear</t>
   </si>
   <si>
-    <t>17. Обновить запись медведя лишними полями</t>
+    <t>16. Обновить запись медведя лишними полями</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 200, в Content - сообщение-подтверждение, запись о медведе должна быть обновлена</t>
   </si>
   <si>
-    <t>18. Создать медведя с пустым payload</t>
-  </si>
-  <si>
-    <t>19. Создать несколько медведей за один запрос</t>
+    <t>17. Создать медведя с пустым payload</t>
+  </si>
+  <si>
+    <t>18. Создать несколько медведей за один запрос</t>
   </si>
   <si>
     <t>payload [{"bear_type":"BLACK","bear_name":"bear_1","bear_age":10}, {"bear_type":"BROWN","bear_name":"bear_2","bear_age":11}]</t>
   </si>
   <si>
-    <t>20. Создать медведя с payload в формате XML</t>
+    <t>19. Создать медведя с payload в формате XML</t>
   </si>
   <si>
     <t>payload &lt;bear&gt;&lt;bear_type&gt;BLACK&lt;/bear_type&gt;&lt;bear_name&gt;Test Name&lt;/bear_name&gt;&lt;bear_age&gt;10&lt;/bear_age&gt;&lt;/bear&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">21. Создать медведя с неправильными заголовками </t>
+    <t xml:space="preserve">20. Создать медведя с неправильными заголовками </t>
   </si>
   <si>
     <t>Content-Type: application/xml</t>
   </si>
   <si>
-    <t>22. Создать медведя с длинным именем</t>
+    <t>21. Создать медведя с длинным именем</t>
   </si>
   <si>
     <t>Ответ: статус код HTTP - 200, в Content - id созданного медведя, медведь должен быть создан с переданными данными</t>
@@ -302,16 +302,16 @@
     <t>payload {"bear_type":"BLACK","bear_name":"Long name","bear_age":17.5}</t>
   </si>
   <si>
-    <t>23. Обновить запись о медведе пустым payload</t>
-  </si>
-  <si>
-    <t>24. Обновить запись медведя списком из нескольких медведей</t>
-  </si>
-  <si>
-    <t>25. Обновить запись медведя с payload в формате XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. Обновить запись медведя с неправильными заголовками </t>
+    <t>22. Обновить запись о медведе пустым payload</t>
+  </si>
+  <si>
+    <t>23. Обновить запись медведя списком из нескольких медведей</t>
+  </si>
+  <si>
+    <t>24. Обновить запись медведя с payload в формате XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Обновить запись медведя с неправильными заголовками </t>
   </si>
 </sst>
 </file>
